--- a/outputs/metrics/model_comparison_metrics.xlsx
+++ b/outputs/metrics/model_comparison_metrics.xlsx
@@ -480,31 +480,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7166123778501629</v>
+        <v>0.7019543973941368</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8022813688212928</v>
+        <v>0.6197718631178707</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3663663663663664</v>
+        <v>0.3373983739837398</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7080536912751678</v>
+        <v>0.6404715127701375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7867093475458495</v>
+        <v>0.7777398632911942</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="H2" t="n">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="I2" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
@@ -517,31 +517,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6775244299674267</v>
+        <v>0.6889250814332247</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6159695817490495</v>
+        <v>0.7908745247148289</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3745173745173745</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.685337726523888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.753772491415077</v>
+        <v>0.7554840596665692</v>
       </c>
       <c r="G3" t="n">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="H3" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="I3" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
@@ -554,31 +554,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6921824104234527</v>
+        <v>0.6872964169381107</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7452471482889734</v>
+        <v>0.7566539923954373</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3836477987421384</v>
+        <v>0.3914373088685015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6745762711864407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7768028338370544</v>
+        <v>0.7648868523393239</v>
       </c>
       <c r="G4" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H4" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I4" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
